--- a/modules/apperp/management-aset/resources/laporan/laporan-penyusutan-aset/standar.xlsx
+++ b/modules/apperp/management-aset/resources/laporan/laporan-penyusutan-aset/standar.xlsx
@@ -7,17 +7,17 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Penyusutan Aset" sheetId="1" r:id="rId4"/>
+    <sheet name="Penyusutan aset" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Penyusutan Aset'!$A$10:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Penyusutan aset'!$A$10:$S$10</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="63">
   <si>
     <t>${kop.logo_kiri}</t>
   </si>
@@ -34,57 +34,57 @@
     <t>${kop.logo_kanan}</t>
   </si>
   <si>
-    <t>Laporan Penyusutan Aset</t>
-  </si>
-  <si>
-    <t>Group Aset</t>
+    <t>Laporan penyusutan aset</t>
+  </si>
+  <si>
+    <t>Periode</t>
+  </si>
+  <si>
+    <t>${filter_periode}</t>
+  </si>
+  <si>
+    <t>Buku</t>
+  </si>
+  <si>
+    <t>${filter_buku}</t>
+  </si>
+  <si>
+    <t>Dicetak</t>
+  </si>
+  <si>
+    <t>${dicetak_pada}</t>
+  </si>
+  <si>
+    <t>Group aset</t>
   </si>
   <si>
     <t>${filter_group}</t>
   </si>
   <si>
-    <t>Golongan</t>
+    <t>Kelompok harta fiskal</t>
   </si>
   <si>
     <t>${filter_golongan}</t>
   </si>
   <si>
-    <t>Jenis Aset</t>
+    <t>Jenis aset</t>
   </si>
   <si>
     <t>${filter_jenis}</t>
   </si>
   <si>
-    <t>Nama Aset</t>
+    <t>Aset</t>
   </si>
   <si>
     <t>${filter_aset}</t>
   </si>
   <si>
-    <t>Periode</t>
-  </si>
-  <si>
-    <t>${filter_periode}</t>
-  </si>
-  <si>
-    <t>Buku</t>
-  </si>
-  <si>
-    <t>${filter_buku}</t>
-  </si>
-  <si>
-    <t>Jumlah Aset</t>
+    <t>Jumlah buku aset</t>
   </si>
   <si>
     <t>${jumlah_aset}</t>
   </si>
   <si>
-    <t>Dicetak</t>
-  </si>
-  <si>
-    <t>${dicetak_pada}</t>
-  </si>
-  <si>
     <t>No.</t>
   </si>
   <si>
@@ -109,61 +109,52 @@
     <t>${baris.spesifikasi}</t>
   </si>
   <si>
-    <t>Group aset</t>
-  </si>
-  <si>
     <t>${baris.group}</t>
   </si>
   <si>
-    <t>Golongan aset</t>
-  </si>
-  <si>
     <t>${baris.golongan}</t>
   </si>
   <si>
-    <t>Jenis aset</t>
-  </si>
-  <si>
     <t>${baris.jenis}</t>
   </si>
   <si>
+    <t>Buku penyusutan</t>
+  </si>
+  <si>
+    <t>${baris.buku}</t>
+  </si>
+  <si>
     <t>Bulan perolehan</t>
   </si>
   <si>
     <t>${baris.bulan_perolehan}</t>
   </si>
   <si>
-    <t>Tahun perolehan</t>
-  </si>
-  <si>
-    <t>${baris.tahun_perolehan}</t>
-  </si>
-  <si>
-    <t>UE (Tahun)</t>
+    <t>Umur ekonomis (tahun)</t>
   </si>
   <si>
     <t>${baris.umur_ekonomis_tahun}</t>
   </si>
   <si>
-    <t>UE (Bulan)</t>
+    <t>Umur ekonomis (bulan)</t>
   </si>
   <si>
     <t>${baris.umur_ekonomis_bulan}</t>
   </si>
   <si>
-    <t>UE Saat Ini</t>
+    <t>Umur berjalan (bulan)</t>
   </si>
   <si>
     <t>${baris.umur_ekonomis_saat_ini}</t>
   </si>
   <si>
-    <t>Sisa UE (Bulan)</t>
+    <t>Sisa umur (bulan)</t>
   </si>
   <si>
     <t>${baris.sisa_umur_ekonomis_bulan}</t>
   </si>
   <si>
-    <t>Persentase penyusutan</t>
+    <t>Tarif per tahun</t>
   </si>
   <si>
     <t>${baris.persentase_penyusutan}</t>
@@ -175,16 +166,16 @@
     <t>${baris.nilai_perolehan}</t>
   </si>
   <si>
-    <t>Penyusutan per tahun</t>
-  </si>
-  <si>
-    <t>${baris.penyusutan_per_tahun}</t>
-  </si>
-  <si>
-    <t>Penyusutan per bulan</t>
-  </si>
-  <si>
-    <t>${baris.penyusutan_per_bulan}</t>
+    <t>Penyusutan bulan ini</t>
+  </si>
+  <si>
+    <t>${baris.penyusutan_bulan_ini}</t>
+  </si>
+  <si>
+    <t>Penyusutan tahun berjalan</t>
+  </si>
+  <si>
+    <t>${baris.penyusutan_tahun_berjalan}</t>
   </si>
   <si>
     <t>Akumulasi penyusutan</t>
@@ -205,10 +196,10 @@
     <t>${total_nilai_perolehan}</t>
   </si>
   <si>
-    <t>${total_penyusutan_tahun}</t>
-  </si>
-  <si>
-    <t>${total_penyusutan_bulan}</t>
+    <t>${total_penyusutan_bulan_ini}</t>
+  </si>
+  <si>
+    <t>${total_penyusutan_tahun_berjalan}</t>
   </si>
   <si>
     <t>${total_akumulasi_penyusutan}</t>
@@ -334,13 +325,13 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -643,20 +634,20 @@
   <dimension ref="A1:S12"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="true" style="0"/>
+    <col min="1" max="1" width="6" customWidth="true" style="0"/>
     <col min="2" max="2" width="16" customWidth="true" style="0"/>
-    <col min="3" max="3" width="28" customWidth="true" style="0"/>
-    <col min="4" max="4" width="26" customWidth="true" style="0"/>
-    <col min="5" max="5" width="16" customWidth="true" style="0"/>
-    <col min="6" max="6" width="16" customWidth="true" style="0"/>
-    <col min="7" max="7" width="16" customWidth="true" style="0"/>
-    <col min="8" max="8" width="16" customWidth="true" style="0"/>
-    <col min="9" max="9" width="16" customWidth="true" style="0"/>
-    <col min="10" max="10" width="16" customWidth="true" style="0"/>
-    <col min="11" max="11" width="16" customWidth="true" style="0"/>
-    <col min="12" max="12" width="16" customWidth="true" style="0"/>
-    <col min="13" max="13" width="16" customWidth="true" style="0"/>
-    <col min="14" max="14" width="16" customWidth="true" style="0"/>
+    <col min="3" max="3" width="30" customWidth="true" style="0"/>
+    <col min="4" max="4" width="28" customWidth="true" style="0"/>
+    <col min="5" max="5" width="18" customWidth="true" style="0"/>
+    <col min="6" max="6" width="18" customWidth="true" style="0"/>
+    <col min="7" max="7" width="18" customWidth="true" style="0"/>
+    <col min="8" max="8" width="18" customWidth="true" style="0"/>
+    <col min="9" max="9" width="15" customWidth="true" style="0"/>
+    <col min="10" max="10" width="12" customWidth="true" style="0"/>
+    <col min="11" max="11" width="12" customWidth="true" style="0"/>
+    <col min="12" max="12" width="12" customWidth="true" style="0"/>
+    <col min="13" max="13" width="12" customWidth="true" style="0"/>
+    <col min="14" max="14" width="11" customWidth="true" style="0"/>
     <col min="15" max="15" width="20" customWidth="true" style="0"/>
     <col min="16" max="16" width="20" customWidth="true" style="0"/>
     <col min="17" max="17" width="20" customWidth="true" style="0"/>
@@ -744,13 +735,13 @@
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E6" t="s">
@@ -764,13 +755,13 @@
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E7" t="s">
@@ -784,73 +775,73 @@
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:19" customHeight="1" ht="32">
+      <c r="A10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="P10" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q10" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="R10" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="S10" s="6" t="s">
-        <v>58</v>
+      <c r="E10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="S10" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -867,82 +858,82 @@
         <v>29</v>
       </c>
       <c r="E11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" t="s">
         <v>31</v>
       </c>
-      <c r="F11" t="s">
-        <v>33</v>
-      </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J11" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="N11" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="O11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="P11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="Q11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="R11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="S11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q12" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="8" t="s">
+      <c r="R12" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="P12" s="8" t="s">
+      <c r="S12" s="8" t="s">
         <v>62</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="S12" s="8" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/modules/apperp/management-aset/resources/laporan/laporan-penyusutan-aset/standar.xlsx
+++ b/modules/apperp/management-aset/resources/laporan/laporan-penyusutan-aset/standar.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="67">
   <si>
     <t>${kop.logo_kiri}</t>
   </si>
@@ -83,6 +83,18 @@
   </si>
   <si>
     <t>${jumlah_aset}</t>
+  </si>
+  <si>
+    <t>Lokasi</t>
+  </si>
+  <si>
+    <t>${filter_lokasi}</t>
+  </si>
+  <si>
+    <t>Kondisi</t>
+  </si>
+  <si>
+    <t>${filter_kondisi}</t>
   </si>
   <si>
     <t>No.</t>
@@ -785,18 +797,32 @@
         <v>21</v>
       </c>
     </row>
+    <row r="9" spans="1:19">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="10" spans="1:19" customHeight="1" ht="32">
       <c r="A10" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>12</v>
@@ -808,104 +834,104 @@
         <v>16</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="M11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="N11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="P11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Q11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="R11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="S11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -921,19 +947,19 @@
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
       <c r="O12" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="S12" s="8" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/modules/apperp/management-aset/resources/laporan/laporan-penyusutan-aset/standar.xlsx
+++ b/modules/apperp/management-aset/resources/laporan/laporan-penyusutan-aset/standar.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="69">
   <si>
     <t>${kop.logo_kiri}</t>
   </si>
@@ -95,6 +95,12 @@
   </si>
   <si>
     <t>${filter_kondisi}</t>
+  </si>
+  <si>
+    <t>Filter tambahan</t>
+  </si>
+  <si>
+    <t>${filter_tambahan}</t>
   </si>
   <si>
     <t>No.</t>
@@ -810,19 +816,25 @@
       <c r="D9" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="10" spans="1:19" customHeight="1" ht="32">
       <c r="A10" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>12</v>
@@ -834,104 +846,104 @@
         <v>16</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Q11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="R11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="S11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -947,19 +959,19 @@
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
       <c r="O12" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="S12" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
